--- a/resources/one-person-ai-business/files/opab-int-leverage-economics.xlsx
+++ b/resources/one-person-ai-business/files/opab-int-leverage-economics.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,11 +67,6 @@
       <color rgb="000C2733"/>
       <sz val="12"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -98,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,8 +118,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -514,7 +507,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>THIS MONTH  (the five-number panel)</t>
+          <t>THIS MONTH  (the six-number panel)</t>
         </is>
       </c>
     </row>
@@ -548,7 +541,6 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
@@ -582,7 +574,6 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -597,7 +588,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
@@ -608,7 +598,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Baseline net revenue (when you started systematising)</t>
+          <t>Baseline net revenue (when you started systematizing)</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -669,7 +659,6 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -687,11 +676,10 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>revenue crept up from delegated demand, not extra founder hours; time freed goes to judgement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
+          <t>revenue crept up from delegated demand, not extra founder hours; time freed goes to judgment.</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
@@ -720,7 +708,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
@@ -734,10 +721,6 @@
           <t>ePORTS — your ecom source. eports.global.</t>
         </is>
       </c>
-    </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="13" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/one-person-ai-business/files/opab-int-leverage-economics.xlsx
+++ b/resources/one-person-ai-business/files/opab-int-leverage-economics.xlsx
@@ -718,7 +718,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
